--- a/scripts/audit/photo_request2.xlsx
+++ b/scripts/audit/photo_request2.xlsx
@@ -77,7 +77,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -91,17 +91,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8F0E1"/>
+        <fgColor rgb="FFFFF4E0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF9F9F9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF4E0"/>
       </patternFill>
     </fill>
     <fill>
@@ -136,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -172,9 +167,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
@@ -557,7 +549,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Запрос фотографий — новые артикулы AWS</t>
+          <t>Запрос фотографий — артикулы AWS без фото</t>
         </is>
       </c>
     </row>
@@ -569,19 +561,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Источник артикулов</t>
+          <t>Критерий</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>stv39.ru (Электроцентр)</t>
+          <t>нет файла в public/img/products (не показывается на сайте)</t>
         </is>
       </c>
     </row>
@@ -592,7 +584,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -606,7 +598,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -692,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -753,251 +745,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  УНО → Выключатели</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>УНО</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>Выключатели</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>U2B-007 black</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>Выключатель звонка 1-кл. чёрный Софт-тач</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>Чёрный</t>
-        </is>
-      </c>
-      <c r="F3" s="9" t="inlineStr">
-        <is>
-          <t>открыть</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr"/>
-      <c r="H3" s="8" t="inlineStr"/>
-      <c r="I3" s="8" t="inlineStr"/>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  УНО → Розетки</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>УНО</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Розетки</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>U1A-016-2 dark grey</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>Розетка RJ45 (cat 5e) 2-я тёмн. серая Софт-тач</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Тёмно-серый</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>открыть</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr"/>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  УНО → Рамки</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>УНО</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Рамки</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>U1A-029-2 white</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Рамка 2-я белая вертикальная Софт-тач</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>Белый</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>открыть</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr"/>
-      <c r="H7" s="8" t="inlineStr"/>
-      <c r="I7" s="8" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>УНО</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>Рамки</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>U2B-029-2 black</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>Рамка 2-я чёрная вертикальная Софт-тач</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>Чёрный</t>
-        </is>
-      </c>
-      <c r="F8" s="11" t="inlineStr">
-        <is>
-          <t>открыть</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr"/>
-      <c r="H8" s="10" t="inlineStr"/>
-      <c r="I8" s="10" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>УНО</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Рамки</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>U1A-031-2 white</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Рамка 3-я белая вертикальная Софт-тач</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Белый</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>открыть</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr"/>
-      <c r="H9" s="8" t="inlineStr"/>
-      <c r="I9" s="8" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>УНО</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>Рамки</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>U2B-031-2 black</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Рамка 3-я чёрная вертикальная Софт-тач</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>Чёрный</t>
-        </is>
-      </c>
-      <c r="F10" s="11" t="inlineStr">
-        <is>
-          <t>открыть</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr"/>
-      <c r="H10" s="10" t="inlineStr"/>
-      <c r="I10" s="10" t="inlineStr"/>
-    </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A6:I6"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId6"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1070,7 +818,7 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  АУРА → Выключатели</t>
         </is>
@@ -1917,7 +1665,7 @@
       <c r="I26" s="10" t="inlineStr"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  АУРА → Розетки</t>
         </is>
@@ -2869,7 +2617,7 @@
       <c r="I54" s="8" t="inlineStr"/>
     </row>
     <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="12" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  АУРА → Рамки</t>
         </is>
@@ -5501,7 +5249,7 @@
       <c r="I130" s="8" t="inlineStr"/>
     </row>
     <row r="131" ht="22" customHeight="1">
-      <c r="A131" s="12" t="inlineStr">
+      <c r="A131" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  АУРА → Прочее</t>
         </is>
@@ -6002,7 +5750,7 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  ДИЗАЙН → Выключатели</t>
         </is>
@@ -6219,7 +5967,7 @@
       <c r="I8" s="10" t="inlineStr"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  ДИЗАЙН → Розетки</t>
         </is>
@@ -6366,7 +6114,7 @@
       <c r="I13" s="10" t="inlineStr"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  ДИЗАЙН → Рамки</t>
         </is>
